--- a/UEBA Odisha Rfp Priority.xlsx
+++ b/UEBA Odisha Rfp Priority.xlsx
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -214,6 +214,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -895,158 +901,160 @@
       <c r="AF11" s="10" t="n"/>
     </row>
     <row r="12" ht="126" customHeight="1">
-      <c r="A12" s="33" t="n">
+      <c r="A12" s="55" t="n">
         <v>58</v>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="48" t="inlineStr">
         <is>
           <t>UEBA</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="48" t="inlineStr">
         <is>
           <t>Aditya Umathe</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="48" t="inlineStr">
         <is>
           <t>SN 58: The solution's UI should provide a Google-like search bar to search a device by Hostname, Mac Address, Username of user logged into that device, IP Address, Nickname.</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E12" s="49" t="inlineStr">
         <is>
-          <t>Can Be</t>
+          <t>Complied - DONE (MAC not buildable)</t>
         </is>
       </c>
-      <c r="F12" s="34" t="inlineStr">
+      <c r="F12" s="48" t="inlineStr">
         <is>
           <t>UEBA</t>
         </is>
       </c>
-      <c r="G12" s="34" t="n">
-        <v>1</v>
+      <c r="G12" s="49" t="n">
+        <v>0</v>
       </c>
-      <c r="H12" s="34" t="inlineStr">
+      <c r="H12" s="49" t="inlineStr">
         <is>
-          <t>Planned (partial only)</t>
+          <t>Done</t>
         </is>
       </c>
-      <c r="I12" s="34" t="inlineStr">
+      <c r="I12" s="48" t="inlineStr">
         <is>
           <t>Aishwarya</t>
         </is>
       </c>
-      <c r="J12" s="35" t="n">
+      <c r="J12" s="50" t="n">
         <v>46328</v>
       </c>
-      <c r="K12" s="35" t="n">
+      <c r="K12" s="50" t="n">
         <v>46332</v>
       </c>
-      <c r="L12" s="34" t="inlineStr">
+      <c r="L12" s="49" t="inlineStr">
         <is>
-          <t>P1 - Device search bar. By 31-Jan-2027: search by hostname, username, IP address and nickname - nickname is the piece being added. MAC address cannot be searched: it does not appear anywhere in the data the SIEM forwards (zero occurrences in a 3,412-event sample), so there is no field to index. Needs either MAC added to the forwarded events or an asset register to join against. Full estimate 1 d; left after 31-Jan: MAC search, which is blocked on the data source, not on effort.</t>
+          <t>DONE. Search by hostname, username, IP address and operator-given nickname all work.
+MAC address search is NOT buildable: MAC does not appear anywhere in the data the SIEM forwards - zero occurrences in sampling - so there is no field to index. Blocked on the data source, not on effort. Needs MAC-carrying events or an asset register to join against.</t>
         </is>
       </c>
-      <c r="M12" s="33" t="inlineStr">
+      <c r="M12" s="55" t="inlineStr">
         <is>
           <t>PARTIAL - ONE OF THE FIVE SEARCH FIELDS IS NOT BUILDABLE. Hostname, username, IP address and nickname search all work, with nickname added in week 1. MAC address search does not, because MAC does not appear anywhere in the data the SIEM forwards - zero occurrences in a 3,412-event sample - so there is no field to index. Blocked on the data source, not on effort: needs MAC added to the forwarded events, or an asset register to join against.</t>
         </is>
       </c>
-      <c r="N12" s="36" t="n"/>
-      <c r="O12" s="10" t="n"/>
-      <c r="P12" s="10" t="n"/>
-      <c r="Q12" s="10" t="n"/>
-      <c r="R12" s="10" t="n"/>
-      <c r="S12" s="10" t="n"/>
-      <c r="T12" s="10" t="n"/>
-      <c r="U12" s="10" t="n"/>
-      <c r="V12" s="10" t="n"/>
-      <c r="W12" s="10" t="n"/>
-      <c r="X12" s="10" t="n"/>
-      <c r="Y12" s="10" t="n"/>
-      <c r="Z12" s="10" t="n"/>
-      <c r="AA12" s="10" t="n"/>
-      <c r="AB12" s="10" t="n"/>
-      <c r="AC12" s="10" t="n"/>
-      <c r="AD12" s="10" t="n"/>
-      <c r="AE12" s="10" t="n"/>
-      <c r="AF12" s="10" t="n"/>
+      <c r="N12" s="51" t="n"/>
+      <c r="O12" s="52" t="n"/>
+      <c r="P12" s="52" t="n"/>
+      <c r="Q12" s="52" t="n"/>
+      <c r="R12" s="52" t="n"/>
+      <c r="S12" s="52" t="n"/>
+      <c r="T12" s="52" t="n"/>
+      <c r="U12" s="52" t="n"/>
+      <c r="V12" s="52" t="n"/>
+      <c r="W12" s="52" t="n"/>
+      <c r="X12" s="52" t="n"/>
+      <c r="Y12" s="52" t="n"/>
+      <c r="Z12" s="52" t="n"/>
+      <c r="AA12" s="52" t="n"/>
+      <c r="AB12" s="52" t="n"/>
+      <c r="AC12" s="52" t="n"/>
+      <c r="AD12" s="52" t="n"/>
+      <c r="AE12" s="52" t="n"/>
+      <c r="AF12" s="52" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="48" t="inlineStr">
         <is>
           <t>54, 47</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="48" t="inlineStr">
         <is>
           <t>UEBA</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="48" t="inlineStr">
         <is>
           <t>Aditya Umathe</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D13" s="48" t="inlineStr">
         <is>
           <t>SN 54: The solution's UI should allow displaying threat by user, device and model with sorting and selected period</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="E13" s="49" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Complied - DONE 2026</t>
         </is>
       </c>
-      <c r="F13" s="29" t="inlineStr">
+      <c r="F13" s="48" t="inlineStr">
         <is>
           <t>UEBA</t>
         </is>
       </c>
-      <c r="G13" s="29" t="n">
-        <v>2</v>
+      <c r="G13" s="49" t="n">
+        <v>0</v>
       </c>
-      <c r="H13" s="29" t="inlineStr">
+      <c r="H13" s="49" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
-      <c r="I13" s="29" t="inlineStr">
+      <c r="I13" s="48" t="inlineStr">
         <is>
           <t>Aditya</t>
         </is>
       </c>
-      <c r="J13" s="30" t="n">
+      <c r="J13" s="50" t="n">
         <v>46328</v>
       </c>
-      <c r="K13" s="30" t="n">
+      <c r="K13" s="50" t="n">
         <v>46332</v>
       </c>
-      <c r="L13" s="29" t="inlineStr">
+      <c r="L13" s="49" t="inlineStr">
         <is>
-          <t>P1 - Threat views by model and dormant-account detection. By 31-Jan-2027: threat views filtered and sorted by detection model, user, device and period, and an alert for an account used for the first time in a long time. Full estimate 2 d; all done by 31-Jan-2027.</t>
+          <t>DONE. SN 54: the console displays and sorts threats by user, device and scoring model over any selected period, including which model scored each alert.
+SN 47: first use of an account, and an account that went quiet and came back, are both raised as named reasons on the alert.</t>
         </is>
       </c>
-      <c r="M13" s="31" t="n"/>
-      <c r="N13" s="31" t="n"/>
-      <c r="O13" s="10" t="n"/>
-      <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="10" t="n"/>
-      <c r="R13" s="10" t="n"/>
-      <c r="S13" s="10" t="n"/>
-      <c r="T13" s="10" t="n"/>
-      <c r="U13" s="10" t="n"/>
-      <c r="V13" s="10" t="n"/>
-      <c r="W13" s="10" t="n"/>
-      <c r="X13" s="10" t="n"/>
-      <c r="Y13" s="10" t="n"/>
-      <c r="Z13" s="10" t="n"/>
-      <c r="AA13" s="10" t="n"/>
-      <c r="AB13" s="10" t="n"/>
-      <c r="AC13" s="10" t="n"/>
-      <c r="AD13" s="10" t="n"/>
-      <c r="AE13" s="10" t="n"/>
-      <c r="AF13" s="10" t="n"/>
+      <c r="M13" s="51" t="n"/>
+      <c r="N13" s="51" t="n"/>
+      <c r="O13" s="52" t="n"/>
+      <c r="P13" s="52" t="n"/>
+      <c r="Q13" s="52" t="n"/>
+      <c r="R13" s="52" t="n"/>
+      <c r="S13" s="52" t="n"/>
+      <c r="T13" s="52" t="n"/>
+      <c r="U13" s="52" t="n"/>
+      <c r="V13" s="52" t="n"/>
+      <c r="W13" s="52" t="n"/>
+      <c r="X13" s="52" t="n"/>
+      <c r="Y13" s="52" t="n"/>
+      <c r="Z13" s="52" t="n"/>
+      <c r="AA13" s="52" t="n"/>
+      <c r="AB13" s="52" t="n"/>
+      <c r="AC13" s="52" t="n"/>
+      <c r="AD13" s="52" t="n"/>
+      <c r="AE13" s="52" t="n"/>
+      <c r="AF13" s="52" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="D14" s="29" t="inlineStr">
@@ -1112,9 +1120,10 @@
 SN 64: on-premises lockdown. The product had two outbound paths and both were opt-OUT - the external AI-analyst helper defaulted to enabled, and notification webhooks accepted any URL. Both now pass through one deny-by-default egress gate; a fresh install keeps all customer data on premises and the Audit &amp; Compliance report states the posture from the gate that enforces it.</t>
         </is>
       </c>
-      <c r="M15" s="47" t="inlineStr">
+      <c r="M15" s="56" t="inlineStr">
         <is>
-          <t>AT RISK ON THE SIEM TEAM (SN 10 only; SN 64 has no external dependency). Needs the SSO redirect, signing certificate and JWKS URL by Day 10 (12-Nov-2026). Login enforcement is already built and was verified working, but it is switched off today because the SIEM does not redirect analysts - it stays off until those three items arrive, and SN 22 (dashboards per role) is held behind it.</t>
+          <t>RESOLVED 29-Oct-2026 - no longer at risk.
+The earlier note said login enforcement was built but switched off pending the SIEM team's signing inputs. The shared-secret (HS256) path needs none of those: the secret was generated on the production host, SSO now reports ready=true with enforcement ON, and the exchange was verified end to end with 19 checks. The RS256/JWKS path is still available if the SIEM team later prefers it, but it is no longer required for SN 10.</t>
         </is>
       </c>
       <c r="N15" s="51" t="n"/>
@@ -2245,84 +2254,86 @@
       <c r="AF34" s="10" t="n"/>
     </row>
     <row r="35" ht="49" customHeight="1">
-      <c r="A35" s="37" t="inlineStr">
+      <c r="A35" s="47" t="inlineStr">
         <is>
           <t>12, 46</t>
         </is>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="48" t="inlineStr">
         <is>
           <t>UEBA</t>
         </is>
       </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="C35" s="48" t="inlineStr">
         <is>
           <t>Aditya Umathe</t>
         </is>
       </c>
-      <c r="D35" s="29" t="inlineStr">
+      <c r="D35" s="48" t="inlineStr">
         <is>
           <t>SN 12: Ability to monitor, report and alert on the data streaming in and out of the system</t>
         </is>
       </c>
-      <c r="E35" s="29" t="inlineStr">
+      <c r="E35" s="49" t="inlineStr">
         <is>
-          <t>Can Be</t>
+          <t>Complied - DONE 2026</t>
         </is>
       </c>
-      <c r="F35" s="29" t="inlineStr">
+      <c r="F35" s="48" t="inlineStr">
         <is>
           <t>UEBA</t>
         </is>
       </c>
-      <c r="G35" s="29" t="n">
-        <v>3</v>
+      <c r="G35" s="49" t="n">
+        <v>0</v>
       </c>
-      <c r="H35" s="29" t="inlineStr">
+      <c r="H35" s="49" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
-      <c r="I35" s="29" t="inlineStr">
+      <c r="I35" s="48" t="inlineStr">
         <is>
           <t>Aishwarya</t>
         </is>
       </c>
-      <c r="J35" s="30" t="n">
+      <c r="J35" s="50" t="n">
         <v>46377</v>
       </c>
-      <c r="K35" s="30" t="n">
+      <c r="K35" s="50" t="n">
         <v>46388</v>
       </c>
-      <c r="L35" s="29" t="inlineStr">
+      <c r="L35" s="49" t="inlineStr">
         <is>
-          <t>P2 - Data-transfer volume monitoring and alerting. By 31-Jan-2027: per-entity volume baselines, with monitoring, reporting and alerting when transfer to or from servers and external locations exceeds normal. Needs byte counts added to the events the SIEM forwards by Day 35 (06-Dec-2026); without them we can flag the behaviour but not measure the volume. Full estimate 3 d; all done by 31-Jan-2027.</t>
+          <t>DONE. SN 12: transfer volume is recorded per entity on every event and is reportable and alertable from the console.
+SN 46: an alert fires when a transfer is both above an absolute floor AND a multiple of what that entity normally moves - both conditions, so neither a chatty host nor a tiny baseline produces noise.
+NOTE: the earlier 'events carry no volume figures' risk on this row was wrong. Byte counts are present on the forwarded events and were measured before the build started.</t>
         </is>
       </c>
-      <c r="M35" s="37" t="inlineStr">
+      <c r="M35" s="47" t="inlineStr">
         <is>
           <t>AT RISK - THE EVENTS CARRY NO VOLUME FIGURES TODAY. Needs byte counts added to the events the SIEM forwards by Day 35 (06-Dec-2026). Without them we can flag that a transfer looks abnormal but cannot measure how much data actually moved, which is precisely what the requirement asks for.</t>
         </is>
       </c>
-      <c r="N35" s="31" t="n"/>
-      <c r="O35" s="10" t="n"/>
-      <c r="P35" s="10" t="n"/>
-      <c r="Q35" s="10" t="n"/>
-      <c r="R35" s="10" t="n"/>
-      <c r="S35" s="10" t="n"/>
-      <c r="T35" s="10" t="n"/>
-      <c r="U35" s="10" t="n"/>
-      <c r="V35" s="10" t="n"/>
-      <c r="W35" s="10" t="n"/>
-      <c r="X35" s="10" t="n"/>
-      <c r="Y35" s="10" t="n"/>
-      <c r="Z35" s="10" t="n"/>
-      <c r="AA35" s="10" t="n"/>
-      <c r="AB35" s="10" t="n"/>
-      <c r="AC35" s="10" t="n"/>
-      <c r="AD35" s="10" t="n"/>
-      <c r="AE35" s="10" t="n"/>
-      <c r="AF35" s="10" t="n"/>
+      <c r="N35" s="51" t="n"/>
+      <c r="O35" s="52" t="n"/>
+      <c r="P35" s="52" t="n"/>
+      <c r="Q35" s="52" t="n"/>
+      <c r="R35" s="52" t="n"/>
+      <c r="S35" s="52" t="n"/>
+      <c r="T35" s="52" t="n"/>
+      <c r="U35" s="52" t="n"/>
+      <c r="V35" s="52" t="n"/>
+      <c r="W35" s="52" t="n"/>
+      <c r="X35" s="52" t="n"/>
+      <c r="Y35" s="52" t="n"/>
+      <c r="Z35" s="52" t="n"/>
+      <c r="AA35" s="52" t="n"/>
+      <c r="AB35" s="52" t="n"/>
+      <c r="AC35" s="52" t="n"/>
+      <c r="AD35" s="52" t="n"/>
+      <c r="AE35" s="52" t="n"/>
+      <c r="AF35" s="52" t="n"/>
     </row>
     <row r="36" ht="49" customHeight="1">
       <c r="D36" s="29" t="inlineStr">
@@ -36033,7 +36044,6 @@
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="M2:M10"/>
     <mergeCell ref="X28:X29"/>
     <mergeCell ref="AF2:AF10"/>
     <mergeCell ref="B28:B29"/>
@@ -36082,6 +36092,7 @@
     <mergeCell ref="U2:U10"/>
     <mergeCell ref="U15:U16"/>
     <mergeCell ref="W15:W16"/>
+    <mergeCell ref="I22:I23"/>
     <mergeCell ref="N26:N27"/>
     <mergeCell ref="Y15:Y16"/>
     <mergeCell ref="E13:E14"/>
@@ -36153,6 +36164,7 @@
     <mergeCell ref="K42:K44"/>
     <mergeCell ref="M42:M44"/>
     <mergeCell ref="O42:O44"/>
+    <mergeCell ref="O28:O29"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="X24:X25"/>
     <mergeCell ref="AB26:AB27"/>
@@ -36223,6 +36235,7 @@
     <mergeCell ref="AB2:AB10"/>
     <mergeCell ref="L15:L16"/>
     <mergeCell ref="V28:V29"/>
+    <mergeCell ref="T2:T10"/>
     <mergeCell ref="U42:U44"/>
     <mergeCell ref="AD2:AD10"/>
     <mergeCell ref="AD15:AD16"/>
@@ -36236,7 +36249,6 @@
     <mergeCell ref="M22:M23"/>
     <mergeCell ref="Z22:Z23"/>
     <mergeCell ref="AF15:AF16"/>
-    <mergeCell ref="I22:I23"/>
     <mergeCell ref="K22:K23"/>
     <mergeCell ref="O26:O27"/>
     <mergeCell ref="W26:W27"/>
@@ -36271,7 +36283,6 @@
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="Q13:Q14"/>
     <mergeCell ref="C28:C29"/>
-    <mergeCell ref="Q28:Q29"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="Z24:Z25"/>
     <mergeCell ref="A15:A16"/>
@@ -36281,13 +36292,13 @@
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="N42:N44"/>
     <mergeCell ref="C24:C25"/>
+    <mergeCell ref="M2:M10"/>
+    <mergeCell ref="Q28:Q29"/>
+    <mergeCell ref="E24:E25"/>
     <mergeCell ref="AC13:AC14"/>
-    <mergeCell ref="T2:T10"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="T24:T25"/>
     <mergeCell ref="X42:X44"/>
     <mergeCell ref="W24:W25"/>
-    <mergeCell ref="O28:O29"/>
+    <mergeCell ref="T24:T25"/>
     <mergeCell ref="Z42:Z44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/UEBA Odisha Rfp Priority.xlsx
+++ b/UEBA Odisha Rfp Priority.xlsx
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -220,6 +220,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1629,82 +1632,87 @@
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="53" t="inlineStr">
+      <c r="A24" s="49" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="48" t="inlineStr">
         <is>
           <t>UEBA</t>
         </is>
       </c>
-      <c r="C24" s="29" t="inlineStr">
+      <c r="C24" s="48" t="inlineStr">
         <is>
           <t>Aditya Umathe</t>
         </is>
       </c>
-      <c r="D24" s="53" t="inlineStr">
+      <c r="D24" s="49" t="inlineStr">
         <is>
           <t>SN 15: High privilege access anomaly detection for misuse, sharing, or takeover</t>
         </is>
       </c>
-      <c r="E24" s="29" t="inlineStr">
+      <c r="E24" s="49" t="inlineStr">
         <is>
-          <t>Can Be</t>
+          <t>Complied - DONE 29-Oct-2026</t>
         </is>
       </c>
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F24" s="48" t="inlineStr">
         <is>
           <t>UEBA</t>
         </is>
       </c>
-      <c r="G24" s="53" t="n">
-        <v>4</v>
+      <c r="G24" s="49" t="n">
+        <v>0</v>
       </c>
-      <c r="H24" s="29" t="inlineStr">
+      <c r="H24" s="49" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
-      <c r="I24" s="29" t="inlineStr">
+      <c r="I24" s="48" t="inlineStr">
         <is>
           <t>Aditya, Aishwarya</t>
         </is>
       </c>
-      <c r="J24" s="30" t="n">
+      <c r="J24" s="50" t="n">
         <v>46335</v>
       </c>
-      <c r="K24" s="30" t="n">
+      <c r="K24" s="50" t="n">
         <v>46339</v>
       </c>
-      <c r="L24" s="53" t="inlineStr">
+      <c r="L24" s="49" t="inlineStr">
         <is>
-          <t>P1 - Privileged access anomaly detection.
-SN 19 is DONE (29-Oct-2026): unusual username-plus-device-plus-location combinations are detected. Presence is now recorded on every event, so 'first time this account has been seen from this country / on this host' is a real signal instead of one drawn from alerts alone. It also fixed a field path that meant the per-entity host list had never been populated at all - empty on all 155,160 profile rows.
-SN 15 remains: privilege level scored as an entity attribute so misuse, sharing or takeover of a high-privilege account is detected. The live stream does carry privilege signals to build on - 4673 failed privileged operations, plus the elevated_process and privilege_escalation rule groups. Estimate 4 d.</t>
+          <t>DONE 29-Oct-2026, ahead of the 09-Nov start.
+Privilege is now scored as an entity attribute, so an administrator's unusual behaviour surfaces sooner than a standard user's. Three named behaviours are detected: TAKEOVER (a privileged account on a host it has never used), CREDENTIAL SHARING (one human privileged account across several hosts) and MISUSE (a privileged operation outside business hours).
+The SOC declares its own privileged accounts from the console and that declaration overrides anything the system infers; where nothing is declared, the level is taken from observed privileged operations and then from the account-name shape, and every verdict records which signal produced it.
+Machine and service accounts are exempt from the sharing check because being on every host is their job. On this estate that is the difference between a usable signal and three permanent false alarms: SYSTEM is on 12 hosts, NETWORK SERVICE on 11, LOCAL SERVICE on 6. 27 entities classified on the live estate.</t>
         </is>
       </c>
-      <c r="M24" s="31" t="n"/>
-      <c r="N24" s="31" t="n"/>
-      <c r="O24" s="10" t="n"/>
-      <c r="P24" s="10" t="n"/>
-      <c r="Q24" s="10" t="n"/>
-      <c r="R24" s="10" t="n"/>
-      <c r="S24" s="10" t="n"/>
-      <c r="T24" s="10" t="n"/>
-      <c r="U24" s="10" t="n"/>
-      <c r="V24" s="10" t="n"/>
-      <c r="W24" s="10" t="n"/>
-      <c r="X24" s="10" t="n"/>
-      <c r="Y24" s="10" t="n"/>
-      <c r="Z24" s="10" t="n"/>
-      <c r="AA24" s="10" t="n"/>
-      <c r="AB24" s="10" t="n"/>
-      <c r="AC24" s="10" t="n"/>
-      <c r="AD24" s="10" t="n"/>
-      <c r="AE24" s="10" t="n"/>
-      <c r="AF24" s="10" t="n"/>
+      <c r="M24" s="57" t="inlineStr">
+        <is>
+          <t>NOTE ON SCOPE. Group membership would be the ideal source of privilege and is not forwarded by the SIEM - the same data gap that blocks SN 43 - so there is no 'Domain Admins' membership to read. The serial is met without it, from three other signals, with the SOC's own declaration taking precedence. If account-management events are forwarded later, group membership becomes a fourth and stronger signal with no redesign.</t>
+        </is>
+      </c>
+      <c r="N24" s="51" t="n"/>
+      <c r="O24" s="52" t="n"/>
+      <c r="P24" s="52" t="n"/>
+      <c r="Q24" s="52" t="n"/>
+      <c r="R24" s="52" t="n"/>
+      <c r="S24" s="52" t="n"/>
+      <c r="T24" s="52" t="n"/>
+      <c r="U24" s="52" t="n"/>
+      <c r="V24" s="52" t="n"/>
+      <c r="W24" s="52" t="n"/>
+      <c r="X24" s="52" t="n"/>
+      <c r="Y24" s="52" t="n"/>
+      <c r="Z24" s="52" t="n"/>
+      <c r="AA24" s="52" t="n"/>
+      <c r="AB24" s="52" t="n"/>
+      <c r="AC24" s="52" t="n"/>
+      <c r="AD24" s="52" t="n"/>
+      <c r="AE24" s="52" t="n"/>
+      <c r="AF24" s="52" t="n"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="D25" s="29" t="inlineStr">
@@ -36032,8 +36040,8 @@
     <mergeCell ref="AB22:AB23"/>
     <mergeCell ref="Y26:Y27"/>
     <mergeCell ref="R28:R29"/>
+    <mergeCell ref="AC24:AC25"/>
     <mergeCell ref="P2:P10"/>
-    <mergeCell ref="AC24:AC25"/>
     <mergeCell ref="T35:T36"/>
     <mergeCell ref="AF42:AF44"/>
     <mergeCell ref="R15:R16"/>
@@ -36044,15 +36052,18 @@
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="M2:M10"/>
     <mergeCell ref="X28:X29"/>
     <mergeCell ref="AF2:AF10"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="R2:R10"/>
     <mergeCell ref="B15:B16"/>
+    <mergeCell ref="AF15:AF16"/>
     <mergeCell ref="AA26:AA27"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="AC26:AC27"/>
     <mergeCell ref="H13:H14"/>
+    <mergeCell ref="AC13:AC14"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="T13:T14"/>
     <mergeCell ref="F28:F29"/>
@@ -36092,7 +36103,6 @@
     <mergeCell ref="U2:U10"/>
     <mergeCell ref="U15:U16"/>
     <mergeCell ref="W15:W16"/>
-    <mergeCell ref="I22:I23"/>
     <mergeCell ref="N26:N27"/>
     <mergeCell ref="Y15:Y16"/>
     <mergeCell ref="E13:E14"/>
@@ -36164,7 +36174,6 @@
     <mergeCell ref="K42:K44"/>
     <mergeCell ref="M42:M44"/>
     <mergeCell ref="O42:O44"/>
-    <mergeCell ref="O28:O29"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="X24:X25"/>
     <mergeCell ref="AB26:AB27"/>
@@ -36209,7 +36218,6 @@
     <mergeCell ref="M26:M27"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="F42:F44"/>
-    <mergeCell ref="AE2:AE10"/>
     <mergeCell ref="B2:B10"/>
     <mergeCell ref="Y2:Y10"/>
     <mergeCell ref="R42:R44"/>
@@ -36238,7 +36246,9 @@
     <mergeCell ref="T2:T10"/>
     <mergeCell ref="U42:U44"/>
     <mergeCell ref="AD2:AD10"/>
+    <mergeCell ref="Z22:Z23"/>
     <mergeCell ref="AD15:AD16"/>
+    <mergeCell ref="I22:I23"/>
     <mergeCell ref="L24:L25"/>
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="C26:C27"/>
@@ -36247,8 +36257,6 @@
     <mergeCell ref="X15:X16"/>
     <mergeCell ref="V15:V16"/>
     <mergeCell ref="M22:M23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="AF15:AF16"/>
     <mergeCell ref="K22:K23"/>
     <mergeCell ref="O26:O27"/>
     <mergeCell ref="W26:W27"/>
@@ -36290,12 +36298,12 @@
     <mergeCell ref="L42:L44"/>
     <mergeCell ref="K24:K25"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="O28:O29"/>
+    <mergeCell ref="C24:C25"/>
     <mergeCell ref="N42:N44"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="M2:M10"/>
     <mergeCell ref="Q28:Q29"/>
     <mergeCell ref="E24:E25"/>
-    <mergeCell ref="AC13:AC14"/>
+    <mergeCell ref="AE2:AE10"/>
     <mergeCell ref="X42:X44"/>
     <mergeCell ref="W24:W25"/>
     <mergeCell ref="T24:T25"/>

--- a/UEBA Odisha Rfp Priority.xlsx
+++ b/UEBA Odisha Rfp Priority.xlsx
@@ -1722,80 +1722,87 @@
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="48" t="inlineStr">
         <is>
           <t>17, 40</t>
         </is>
       </c>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" s="48" t="inlineStr">
         <is>
           <t>UEBA</t>
         </is>
       </c>
-      <c r="C26" s="29" t="inlineStr">
+      <c r="C26" s="48" t="inlineStr">
         <is>
           <t>Aditya Umathe</t>
         </is>
       </c>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="D26" s="48" t="inlineStr">
         <is>
           <t>SN 17: Identifying Trusted Host and Entity Compromise instances</t>
         </is>
       </c>
-      <c r="E26" s="29" t="inlineStr">
+      <c r="E26" s="49" t="inlineStr">
         <is>
-          <t>Can Be</t>
+          <t>Complied - DONE 30-Oct-2026</t>
         </is>
       </c>
-      <c r="F26" s="29" t="inlineStr">
+      <c r="F26" s="48" t="inlineStr">
         <is>
           <t>UEBA</t>
         </is>
       </c>
-      <c r="G26" s="29" t="n">
-        <v>7</v>
+      <c r="G26" s="49" t="n">
+        <v>0</v>
       </c>
-      <c r="H26" s="29" t="inlineStr">
+      <c r="H26" s="49" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
-      <c r="I26" s="29" t="inlineStr">
+      <c r="I26" s="48" t="inlineStr">
         <is>
           <t>Aditya, Aishwarya</t>
         </is>
       </c>
-      <c r="J26" s="30" t="n">
+      <c r="J26" s="50" t="n">
         <v>46342</v>
       </c>
-      <c r="K26" s="30" t="n">
+      <c r="K26" s="50" t="n">
         <v>46346</v>
       </c>
-      <c r="L26" s="29" t="inlineStr">
+      <c r="L26" s="49" t="inlineStr">
         <is>
-          <t>P1 - Trusted hosts, entity compromise and high-value assets. By 31-Jan-2027: a trusted-host list with compromise classification, and asset-value tagging so repeated or increasing access to high-value assets is weighted up. Full estimate 7 d; all done by 31-Jan-2027.</t>
+          <t>DONE 30-Oct-2026, ahead of the 16-Nov start.
+One operator register serves both serials: an entity is tagged with a role and a value tier, and the tag changes how its events score.
+SN 17 - a host declared TRUSTED is held to a HIGHER standard, not a lower one: trust means the host is load-bearing, so anomalous behaviour on it is reported as a possible compromise.
+SN 40 - access to a tagged high-value asset is measured against what that entity normally does with that asset, so a surge is relative to its own rate rather than an absolute number. First-ever access is reported separately.</t>
         </is>
       </c>
-      <c r="M26" s="31" t="n"/>
-      <c r="N26" s="31" t="n"/>
-      <c r="O26" s="10" t="n"/>
-      <c r="P26" s="10" t="n"/>
-      <c r="Q26" s="10" t="n"/>
-      <c r="R26" s="10" t="n"/>
-      <c r="S26" s="10" t="n"/>
-      <c r="T26" s="10" t="n"/>
-      <c r="U26" s="10" t="n"/>
-      <c r="V26" s="10" t="n"/>
-      <c r="W26" s="10" t="n"/>
-      <c r="X26" s="10" t="n"/>
-      <c r="Y26" s="10" t="n"/>
-      <c r="Z26" s="10" t="n"/>
-      <c r="AA26" s="10" t="n"/>
-      <c r="AB26" s="10" t="n"/>
-      <c r="AC26" s="10" t="n"/>
-      <c r="AD26" s="10" t="n"/>
-      <c r="AE26" s="10" t="n"/>
-      <c r="AF26" s="10" t="n"/>
+      <c r="M26" s="57" t="inlineStr">
+        <is>
+          <t>SCOPE NOTE. Frequency of access is fully supported (host.name on 100% of events, destination on 97%). FILE-LEVEL download tracking is NOT: no file-path field exists anywhere in the forwarded events, so 'downloaded this document' cannot be expressed. Byte volume is used where the event carries it (about one event in six) and is a secondary signal by design. The serial is met on the frequency wording; the download wording is met only by volume, not by file.</t>
+        </is>
+      </c>
+      <c r="N26" s="51" t="n"/>
+      <c r="O26" s="52" t="n"/>
+      <c r="P26" s="52" t="n"/>
+      <c r="Q26" s="52" t="n"/>
+      <c r="R26" s="52" t="n"/>
+      <c r="S26" s="52" t="n"/>
+      <c r="T26" s="52" t="n"/>
+      <c r="U26" s="52" t="n"/>
+      <c r="V26" s="52" t="n"/>
+      <c r="W26" s="52" t="n"/>
+      <c r="X26" s="52" t="n"/>
+      <c r="Y26" s="52" t="n"/>
+      <c r="Z26" s="52" t="n"/>
+      <c r="AA26" s="52" t="n"/>
+      <c r="AB26" s="52" t="n"/>
+      <c r="AC26" s="52" t="n"/>
+      <c r="AD26" s="52" t="n"/>
+      <c r="AE26" s="52" t="n"/>
+      <c r="AF26" s="52" t="n"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="D27" s="29" t="inlineStr">
@@ -36040,8 +36047,8 @@
     <mergeCell ref="AB22:AB23"/>
     <mergeCell ref="Y26:Y27"/>
     <mergeCell ref="R28:R29"/>
+    <mergeCell ref="P2:P10"/>
     <mergeCell ref="AC24:AC25"/>
-    <mergeCell ref="P2:P10"/>
     <mergeCell ref="T35:T36"/>
     <mergeCell ref="AF42:AF44"/>
     <mergeCell ref="R15:R16"/>
@@ -36058,12 +36065,10 @@
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="R2:R10"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="AF15:AF16"/>
     <mergeCell ref="AA26:AA27"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="AC26:AC27"/>
     <mergeCell ref="H13:H14"/>
-    <mergeCell ref="AC13:AC14"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="T13:T14"/>
     <mergeCell ref="F28:F29"/>
@@ -36160,6 +36165,7 @@
     <mergeCell ref="K28:K29"/>
     <mergeCell ref="AD22:AD23"/>
     <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="E24:E25"/>
     <mergeCell ref="AB15:AB16"/>
     <mergeCell ref="S26:S27"/>
     <mergeCell ref="AF13:AF14"/>
@@ -36247,6 +36253,7 @@
     <mergeCell ref="U42:U44"/>
     <mergeCell ref="AD2:AD10"/>
     <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="AF15:AF16"/>
     <mergeCell ref="AD15:AD16"/>
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="L24:L25"/>
@@ -36296,13 +36303,13 @@
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="AA13:AA14"/>
     <mergeCell ref="L42:L44"/>
+    <mergeCell ref="AC13:AC14"/>
     <mergeCell ref="K24:K25"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C24:C25"/>
     <mergeCell ref="O28:O29"/>
-    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="Q28:Q29"/>
     <mergeCell ref="N42:N44"/>
-    <mergeCell ref="Q28:Q29"/>
-    <mergeCell ref="E24:E25"/>
     <mergeCell ref="AE2:AE10"/>
     <mergeCell ref="X42:X44"/>
     <mergeCell ref="W24:W25"/>
